--- a/SuppXLS/Scen_RES_SHARE_50%_ANNUAL.xlsx
+++ b/SuppXLS/Scen_RES_SHARE_50%_ANNUAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="Ten_skoroszyt" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda2\Veda_models\MSc_SELECT_FULL\SuppXLS\Policy_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda2\Veda_models\MSc_SELECT_2026\MSc_SELECT-main\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53BBC11-87F8-4059-91D9-64376CEA248E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F4C40F-9129-48F9-B088-21BAF5A3949F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,19 +58,10 @@
     <t>UC_FLO</t>
   </si>
   <si>
-    <t>UC_RHSRTS~2030</t>
-  </si>
-  <si>
     <t>UC_RHSRTS~0</t>
   </si>
   <si>
     <t>UC_Desc</t>
-  </si>
-  <si>
-    <t>UC_RHSRTS~2035</t>
-  </si>
-  <si>
-    <t>UC_RHSRTS~2040</t>
   </si>
   <si>
     <t>UC_RES_50_ANNUAL</t>
@@ -136,13 +127,22 @@
     <t xml:space="preserve"> ENTSO data points</t>
   </si>
   <si>
-    <t>UC_RHSRTS~2045</t>
+    <t>Coppied from VT_MODEL_DMD_V01:</t>
   </si>
   <si>
-    <t>UC_RHSRTS~2050</t>
+    <t>UC_RHSRT~2030</t>
   </si>
   <si>
-    <t>Coppied from VT_MODEL_DMD_V01:</t>
+    <t>UC_RHSRT~2035</t>
+  </si>
+  <si>
+    <t>UC_RHSRT~2040</t>
+  </si>
+  <si>
+    <t>UC_RHSRT~2045</t>
+  </si>
+  <si>
+    <t>UC_RHSRT~2050</t>
   </si>
 </sst>
 </file>
@@ -4043,9 +4043,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="43" borderId="18" xfId="1114" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="190" fontId="17" fillId="46" borderId="20" xfId="1060" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4059,9 +4056,6 @@
     <xf numFmtId="190" fontId="24" fillId="47" borderId="22" xfId="1060" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="190" fontId="24" fillId="47" borderId="22" xfId="1060" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="191" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4084,6 +4078,12 @@
     </xf>
     <xf numFmtId="3" fontId="17" fillId="43" borderId="18" xfId="1116" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="190" fontId="17" fillId="46" borderId="20" xfId="1060" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="24" fillId="47" borderId="22" xfId="1060" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2202">
@@ -6318,8 +6318,8 @@
       <xdr:rowOff>110957</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="7811754" cy="624530"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="pole tekstowe 5">
@@ -6798,7 +6798,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="pole tekstowe 5">
@@ -7167,7 +7167,7 @@
   <sheetData>
     <row r="2" spans="2:21" ht="15" customHeight="1">
       <c r="B2" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>0</v>
@@ -7231,90 +7231,90 @@
         <v>7</v>
       </c>
       <c r="G6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="14" t="s">
+      <c r="M6" s="13" t="s">
         <v>9</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="2:21" ht="47.25" customHeight="1" thickBot="1">
       <c r="B7" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="F7" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="G7" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="M7" s="15" t="s">
         <v>22</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="15" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8" spans="2:21" ht="42" customHeight="1" thickBot="1">
       <c r="B8" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>16</v>
-      </c>
       <c r="E8" s="12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F8" s="12">
         <v>1</v>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="30">
         <f>0.5*G22</f>
         <v>282.60000000000002</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="30">
         <f t="shared" ref="H8:K8" si="0">0.5*H22</f>
         <v>349.01712328767064</v>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="30">
         <f t="shared" si="0"/>
         <v>414</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="30">
         <f t="shared" si="0"/>
         <v>476.97493150684971</v>
       </c>
-      <c r="K8" s="32">
+      <c r="K8" s="30">
         <f t="shared" si="0"/>
         <v>540.95383561644087</v>
       </c>
@@ -7328,177 +7328,177 @@
     </row>
     <row r="17" spans="3:11">
       <c r="D17" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="3:11">
-      <c r="C19" s="18"/>
-      <c r="D19" s="19"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="3:11">
-      <c r="D20" s="20" t="s">
-        <v>26</v>
+      <c r="D20" s="19" t="s">
+        <v>23</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="20">
         <v>2023</v>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="20">
         <v>2025</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="20">
         <v>2030</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="20">
         <v>2035</v>
       </c>
-      <c r="I20" s="21">
+      <c r="I20" s="20">
         <v>2040</v>
       </c>
-      <c r="J20" s="21">
+      <c r="J20" s="20">
         <v>2045</v>
       </c>
-      <c r="K20" s="21">
+      <c r="K20" s="20">
         <v>2050</v>
       </c>
     </row>
     <row r="21" spans="3:11" ht="38.25" customHeight="1">
-      <c r="D21" s="22" t="s">
-        <v>27</v>
+      <c r="D21" s="21" t="s">
+        <v>24</v>
       </c>
-      <c r="E21" s="23" t="s">
-        <v>28</v>
+      <c r="E21" s="32" t="s">
+        <v>25</v>
       </c>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
     </row>
     <row r="22" spans="3:11">
       <c r="D22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="22">
         <f t="shared" ref="E22:K22" si="1">E27*3.6</f>
         <v>393.80400000000003</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="22">
         <f t="shared" si="1"/>
         <v>442.11863013698968</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="22">
         <f t="shared" si="1"/>
         <v>565.20000000000005</v>
       </c>
-      <c r="H22" s="24">
+      <c r="H22" s="22">
         <f t="shared" si="1"/>
         <v>698.03424657534129</v>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="22">
         <f t="shared" si="1"/>
         <v>828</v>
       </c>
-      <c r="J22" s="24">
+      <c r="J22" s="22">
         <f t="shared" si="1"/>
         <v>953.94986301369943</v>
       </c>
-      <c r="K22" s="24">
+      <c r="K22" s="22">
         <f t="shared" si="1"/>
         <v>1081.9076712328817</v>
       </c>
     </row>
     <row r="23" spans="3:11">
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
     </row>
     <row r="24" spans="3:11">
-      <c r="E24" s="26" t="s">
-        <v>30</v>
+      <c r="E24" s="24" t="s">
+        <v>27</v>
       </c>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
     </row>
     <row r="25" spans="3:11">
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
     </row>
     <row r="26" spans="3:11">
-      <c r="E26" s="21">
+      <c r="E26" s="20">
         <v>2023</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="20">
         <v>2025</v>
       </c>
-      <c r="G26" s="21">
+      <c r="G26" s="20">
         <v>2030</v>
       </c>
-      <c r="H26" s="21">
+      <c r="H26" s="20">
         <v>2035</v>
       </c>
-      <c r="I26" s="21">
+      <c r="I26" s="20">
         <v>2040</v>
       </c>
-      <c r="J26" s="21">
+      <c r="J26" s="20">
         <v>2045</v>
       </c>
-      <c r="K26" s="21">
+      <c r="K26" s="20">
         <v>2050</v>
       </c>
     </row>
     <row r="27" spans="3:11">
-      <c r="D27" s="27" t="s">
-        <v>31</v>
+      <c r="D27" s="25" t="s">
+        <v>28</v>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="26">
         <v>109.39</v>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="27">
         <f>_xlfn.FORECAST.LINEAR(2025,{109.39;157;230}, {2023;2030;2040})</f>
         <v>122.81073059360824</v>
       </c>
-      <c r="G27" s="28">
+      <c r="G27" s="26">
         <v>157</v>
       </c>
-      <c r="H27" s="29">
+      <c r="H27" s="27">
         <f>_xlfn.FORECAST.LINEAR(2035,{109.39;157;230}, {2023;2030;2040})</f>
         <v>193.89840182648368</v>
       </c>
-      <c r="I27" s="28">
+      <c r="I27" s="26">
         <v>230</v>
       </c>
-      <c r="J27" s="29">
+      <c r="J27" s="27">
         <f>_xlfn.FORECAST.LINEAR(2045,{109.39;157;230}, {2023;2030;2040})</f>
         <v>264.98607305936093</v>
       </c>
-      <c r="K27" s="29">
+      <c r="K27" s="27">
         <f>_xlfn.FORECAST.LINEAR(2050,{109.39;157;230}, {2023;2030;2040})</f>
         <v>300.52990867580047</v>
       </c>
     </row>
     <row r="29" spans="3:11">
-      <c r="E29" s="30" t="s">
-        <v>32</v>
+      <c r="E29" s="28" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="3:11">
-      <c r="E30" s="31"/>
-      <c r="F30" s="27" t="s">
-        <v>33</v>
+      <c r="E30" s="29"/>
+      <c r="F30" s="25" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -7524,6 +7524,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="12" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="5ae10a33478425c8b0682342cd902bb6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d4d464c5e04a95514152bf5b8c9c7854" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
@@ -7742,17 +7753,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F91B0505-87C0-4533-9D1B-20F030974763}">
   <ds:schemaRefs>
@@ -7762,6 +7762,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1414681-578E-43B8-8934-BC5759CBC3B5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9690AA4-2973-4C8B-AFF5-174A0EBF4012}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7778,15 +7789,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1414681-578E-43B8-8934-BC5759CBC3B5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/SuppXLS/Scen_RES_SHARE_50%_ANNUAL.xlsx
+++ b/SuppXLS/Scen_RES_SHARE_50%_ANNUAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda2\Veda_models\MSc_SELECT_2026\MSc_SELECT-main\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F4C40F-9129-48F9-B088-21BAF5A3949F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAC8148-7458-4C19-BBD4-8813B89858F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,12 +33,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
-  <si>
-    <t>Wymagana minimalna produkcja energii elektrycznej z OZE [PJ]</t>
-  </si>
-  <si>
-    <t>~UC_Sets: T_E:</t>
-  </si>
   <si>
     <t>~UC_T</t>
   </si>
@@ -65,9 +59,6 @@
   </si>
   <si>
     <t>UC_RES_50_ANNUAL</t>
-  </si>
-  <si>
-    <t>~UC_SETS: R_E: NL</t>
   </si>
   <si>
     <t>ELC_FIN_DEM</t>
@@ -144,6 +135,50 @@
   <si>
     <t>UC_RHSRT~2050</t>
   </si>
+  <si>
+    <t>Required minimum electricity production from renewable energy sources (RES) [PJ]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">~UC_Sets: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>T_E:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>~UC_Sets:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve"> R_E:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> NL</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -181,7 +216,7 @@
     <numFmt numFmtId="190" formatCode="\Te\x\t"/>
     <numFmt numFmtId="191" formatCode="0.0"/>
   </numFmts>
-  <fonts count="116">
+  <fonts count="117">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -932,6 +967,14 @@
       <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="50">
@@ -7167,10 +7210,10 @@
   <sheetData>
     <row r="2" spans="2:21" ht="15" customHeight="1">
       <c r="B2" s="6" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -7183,7 +7226,7 @@
     </row>
     <row r="3" spans="2:21" ht="15" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -7205,7 +7248,7 @@
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="8" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="7"/>
@@ -7216,84 +7259,84 @@
     </row>
     <row r="6" spans="2:21" ht="31.7" customHeight="1">
       <c r="B6" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="E6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="F6" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="G6" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="M6" s="13" t="s">
         <v>7</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="2:21" ht="47.25" customHeight="1" thickBot="1">
       <c r="B7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="F7" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="G7" s="31" t="s">
         <v>17</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="31" t="s">
-        <v>20</v>
       </c>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="J7" s="31"/>
       <c r="K7" s="31"/>
       <c r="L7" s="15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="2:21" ht="42" customHeight="1" thickBot="1">
       <c r="B8" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>13</v>
-      </c>
       <c r="E8" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F8" s="12">
         <v>1</v>
@@ -7328,7 +7371,7 @@
     </row>
     <row r="17" spans="3:11">
       <c r="D17" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="3:11">
@@ -7337,7 +7380,7 @@
     </row>
     <row r="20" spans="3:11">
       <c r="D20" s="19" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E20" s="20">
         <v>2023</v>
@@ -7363,10 +7406,10 @@
     </row>
     <row r="21" spans="3:11" ht="38.25" customHeight="1">
       <c r="D21" s="21" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
@@ -7377,7 +7420,7 @@
     </row>
     <row r="22" spans="3:11">
       <c r="D22" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E22" s="22">
         <f t="shared" ref="E22:K22" si="1">E27*3.6</f>
@@ -7419,7 +7462,7 @@
     </row>
     <row r="24" spans="3:11">
       <c r="E24" s="24" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F24" s="23"/>
       <c r="G24" s="23"/>
@@ -7462,7 +7505,7 @@
     </row>
     <row r="27" spans="3:11">
       <c r="D27" s="25" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E27" s="26">
         <v>109.39</v>
@@ -7492,13 +7535,13 @@
     </row>
     <row r="29" spans="3:11">
       <c r="E29" s="28" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="3:11">
       <c r="E30" s="29"/>
       <c r="F30" s="25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -7524,17 +7567,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="12" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="5ae10a33478425c8b0682342cd902bb6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d4d464c5e04a95514152bf5b8c9c7854" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
@@ -7753,6 +7785,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F91B0505-87C0-4533-9D1B-20F030974763}">
   <ds:schemaRefs>
@@ -7762,17 +7805,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1414681-578E-43B8-8934-BC5759CBC3B5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9690AA4-2973-4C8B-AFF5-174A0EBF4012}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7789,4 +7821,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1414681-578E-43B8-8934-BC5759CBC3B5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>